--- a/Result/profitability/3563.xlsx
+++ b/Result/profitability/3563.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.12</v>
       </c>
       <c r="M2" t="n">
-        <v>3.27875</v>
+        <v>3.85375</v>
       </c>
       <c r="N2" t="n">
-        <v>59.0525</v>
+        <v>60.33374999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2125</v>
+        <v>3.4975</v>
       </c>
       <c r="N3" t="n">
-        <v>59.33125</v>
+        <v>58.80625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.855</v>
+        <v>2.85125</v>
       </c>
       <c r="N4" t="n">
-        <v>57.09</v>
+        <v>56.5975</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>2.20375</v>
+        <v>2.32875</v>
       </c>
       <c r="N5" t="n">
-        <v>55.6825</v>
+        <v>55.205</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>1.6875</v>
+        <v>1.85375</v>
       </c>
       <c r="N6" t="n">
-        <v>55.3675</v>
+        <v>55.97125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>1.25875</v>
+        <v>1.44125</v>
       </c>
       <c r="N7" t="n">
-        <v>54.735</v>
+        <v>54.80375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.55</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8612500000000001</v>
+        <v>0.9337500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>55.14625</v>
+        <v>55.125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9572,6 +9572,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3563</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1047</v>
+      </c>
+      <c r="D73" t="n">
+        <v>415</v>
+      </c>
+      <c r="E73" t="n">
+        <v>633</v>
+      </c>
+      <c r="F73" t="n">
+        <v>60.41</v>
+      </c>
+      <c r="G73" t="n">
+        <v>409</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>39.05%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>16</v>
+      </c>
+      <c r="J73" t="n">
+        <v>425</v>
+      </c>
+      <c r="K73" t="n">
+        <v>332</v>
+      </c>
+      <c r="L73" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="M73" t="n">
+        <v>3.7875</v>
+      </c>
+      <c r="N73" t="n">
+        <v>59.9725</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0.1258134490238612</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>-0.1700000000000017</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>-0.002806206668867661</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0.2386634844868736</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>-3.820000000000007</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>-0.05947376615288813</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
